--- a/data/por_departamento/Sonsonate/establecimientos_salud.xlsx
+++ b/data/por_departamento/Sonsonate/establecimientos_salud.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benjamin.escalante\Desktop\Unidades de Salud\gis-unidades-salud\data\por_departamento\Sonsonate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CADE05-6521-4273-8931-59F255F1B016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF405BC-9507-4D74-A66A-84619E5C8FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/por_departamento/Sonsonate/establecimientos_salud.xlsx
+++ b/data/por_departamento/Sonsonate/establecimientos_salud.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benjamin.escalante\Desktop\Unidades de Salud\gis-unidades-salud\data\por_departamento\Sonsonate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF405BC-9507-4D74-A66A-84619E5C8FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20782BFD-90D1-4684-A90F-6637CB94818B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
